--- a/Result/profitability/4770.xlsx
+++ b/Result/profitability/4770.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM28"/>
+  <dimension ref="A1:AM29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3986,6 +3986,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4770</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1305</v>
+      </c>
+      <c r="D29" t="n">
+        <v>840</v>
+      </c>
+      <c r="E29" t="n">
+        <v>465</v>
+      </c>
+      <c r="F29" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="G29" t="n">
+        <v>300</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>22.97%</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>18</v>
+      </c>
+      <c r="J29" t="n">
+        <v>318</v>
+      </c>
+      <c r="K29" t="n">
+        <v>249</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.29625</v>
+      </c>
+      <c r="N29" t="n">
+        <v>34.94625</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.5899999999999999</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.234126984126984</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.6799999999999997</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.01946193474527758</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.3599999999999999</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.1309090909090909</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-1.740000000000002</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>-0.04657387580299788</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
